--- a/5. version_manager/PDC_Version_Manager_Requirements.xlsx
+++ b/5. version_manager/PDC_Version_Manager_Requirements.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_문서정보" sheetId="1" r:id="Re9f3da68a63b4dff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_시스템개요" sheetId="2" r:id="Ra8689b0b044a4c34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_저장소구조" sheetId="3" r:id="Rb04853675ea3450e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_기능요구사항" sheetId="4" r:id="R549a14f8dbd14661"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_안전요구사항" sheetId="5" r:id="R2b6e1b077d574266"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_버전관리규칙" sheetId="6" r:id="R8fd7071b9bc34a41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_자기업데이트" sheetId="7" r:id="R3c5c92a5a74146ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_UI요구사항" sheetId="8" r:id="R8c0a2c3ec5c44fdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_운영절차" sheetId="9" r:id="Rfb3a4250474a4bc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_검증시나리오" sheetId="10" r:id="R62ff3ff4757a4e73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_변경이력" sheetId="11" r:id="R7e769d69c6b1454b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_AI변경원칙" sheetId="12" r:id="R8ee2ddac278b4804"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_문서정보" sheetId="1" r:id="R806a88c16d514ecc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_시스템개요" sheetId="2" r:id="R14469a1299df4d09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_저장소구조" sheetId="3" r:id="Radf234dc0a8b4ca6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_기능요구사항" sheetId="4" r:id="R9a23f9dc210f4e49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_안전요구사항" sheetId="5" r:id="Rdff3727c5a2b4e69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_버전관리규칙" sheetId="6" r:id="R9e4563b90a694210"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_자기업데이트" sheetId="7" r:id="R65f5cefc28f142fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_UI요구사항" sheetId="8" r:id="R99723572663448de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_운영절차" sheetId="9" r:id="R9e9d8ca4a1ad451e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_검증시나리오" sheetId="10" r:id="Rb8cabf66c5bc42b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_변경이력" sheetId="11" r:id="Re9bc63956e174f8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_AI변경원칙" sheetId="12" r:id="R571fa1f0da4d46a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -419,7 +419,7 @@
         <x:v>문서 버전</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>260809_3</x:v>
+        <x:v>260810_1</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -443,7 +443,7 @@
         <x:v>Release 패키지</x:v>
       </x:c>
       <x:c r="B8" s="13" t="str">
-        <x:v>PDC_Version_Manager_260809_3.zip</x:v>
+        <x:v>PDC_Version_Manager_260810_1.zip</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -467,7 +467,7 @@
         <x:v>목적</x:v>
       </x:c>
       <x:c r="B11" s="13" t="str">
-        <x:v>여러 PC에서 PDC 프로그램/파일의 Git 기반 형상관리, Push/Pull, 이력/Tag 관리 및 Version Manager 자체 업데이트를 안전하게 자동화한다.</x:v>
+        <x:v>여러 PC에서 '자동화 프로그램' Repository 전체(1~6번 폴더 및 루트 실행기)의 Git 기반 형상관리, Pull/Commit/Push, 이력/Tag 관리 및 Version Manager 자체 업데이트를 안전하게 자동화한다.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -747,6 +747,40 @@
         <x:v>REP-012,UPD-012,UPD-014</x:v>
       </x:c>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="13" t="str">
+        <x:v>TC-013</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="str">
+        <x:v>6번 BoardRepo 포함 Push/Pull</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="str">
+        <x:v>6. boardrepo/current 또는 BoardRepo.pyw 변경 → Commit+Push → 별도 Clone에서 Pull</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="str">
+        <x:v>BoardRepo 관련 변경까지 다른 Clone에 동일하게 반영된다.</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="str">
+        <x:v>REP-015,REP-016,FR-015</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="13" t="str">
+        <x:v>TC-014</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="str">
+        <x:v>공용 1~4번 Repository 동기화</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>공용 1~4번 중 하나의 파일 변경 → Commit+Push → 다른 Clone Pull</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="str">
+        <x:v>변경 파일이 동일 위치의 공용 1~4번 폴더에 반영된다.</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="str">
+        <x:v>REP-017,FR-015</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
@@ -843,6 +877,20 @@
         <x:v>Update ZIP 해제 시 루트에는 PDC_Version_Manager.py만 노출하고, Release ZIP/요구사항 Excel은 5. version_manager에 배치. 중복 README/Release Rule TXT 제거 및 요구사항 Excel 단일 기준 문서화.</x:v>
       </x:c>
     </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="str">
+        <x:v>260810_1</x:v>
+      </x:c>
+      <x:c r="B8" s="13" t="str">
+        <x:v>2026-08-10</x:v>
+      </x:c>
+      <x:c r="C8" s="13" t="str">
+        <x:v>자동화 프로그램 통합</x:v>
+      </x:c>
+      <x:c r="D8" s="13" t="str">
+        <x:v>Repository Root를 '자동화 프로그램'으로 통합하는 운영 구조 추가. 6. boardrepo, 루트 BoardRepo Launcher, 공용 1~4번 자료 폴더, Repository 전체 Push/Pull 요구사항 추가.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:D1"/>
@@ -1006,6 +1054,20 @@
         <x:v>향후 Release/Update ZIP 생성 시 REP-011~013, UPD-012~014의 구조를 유지하고 사용자의 명시적 요청 없이 루트에 보조 TXT/문서를 추가하지 않는다.</x:v>
       </x:c>
       <x:c r="D12" s="13" t="str">
+        <x:v>필수</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="13" t="str">
+        <x:v>AI-010</x:v>
+      </x:c>
+      <x:c r="B13" s="13" t="str">
+        <x:v>통합 구조 보존</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="str">
+        <x:v>향후 수정 시 1~4번 공용자료, 5.version_manager, 6.boardrepo, 루트 PDC_Version_Manager.py/BoardRepo.pyw 구조를 기준선으로 유지하며 사용자 요청 없이 다시 이중화하지 않는다.</x:v>
+      </x:c>
+      <x:c r="D13" s="13" t="str">
         <x:v>필수</x:v>
       </x:c>
     </x:row>
@@ -1427,6 +1489,74 @@
         <x:v>5번 폴더 내용 확인</x:v>
       </x:c>
     </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="13" t="str">
+        <x:v>REP-014</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="str">
+        <x:v>통합 Root 명칭</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>통합 운영의 권장 최상위 폴더명은 '자동화 프로그램'으로 한다. 단, 코드 동작은 폴더명 자체를 절대경로로 하드코딩하지 않는다.</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="str">
+        <x:v>SHOULD</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="str">
+        <x:v>폴더명 변경/Clone 시험</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="13" t="str">
+        <x:v>REP-015</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="str">
+        <x:v>BoardRepo 관리 폴더</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="str">
+        <x:v>Repository Root에는 6. boardrepo 폴더를 두고 BoardRepo Release ZIP, 최신 요구사항 Excel 및 current 런타임을 관리한다.</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="str">
+        <x:v>MUST</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="str">
+        <x:v>6. boardrepo 구조 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="13" t="str">
+        <x:v>REP-016</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="str">
+        <x:v>루트 실행기</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="str">
+        <x:v>Repository Root에는 PDC_Version_Manager.py와 BoardRepo.pyw를 사용자 실행용 파일로 둘 수 있으며, 실제 BoardRepo 구현은 6. boardrepo/current에 분리한다.</x:v>
+      </x:c>
+      <x:c r="D19" s="13" t="str">
+        <x:v>MUST</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="str">
+        <x:v>루트 파일/6번 current 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="13" t="str">
+        <x:v>REP-017</x:v>
+      </x:c>
+      <x:c r="B20" s="13" t="str">
+        <x:v>공용 1~4번</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="str">
+        <x:v>1. PassFail, 2. SignalExport, 3. Ext, 4. Backup은 Git 동기화와 BoardRepo 업로드/다운로드가 함께 사용하는 단일 공용 자료 폴더로 유지한다.</x:v>
+      </x:c>
+      <x:c r="D20" s="13" t="str">
+        <x:v>MUST</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="str">
+        <x:v>중복 자료 폴더 부재 확인</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
@@ -1715,6 +1845,23 @@
         <x:v>신규 설정 환경 실행</x:v>
       </x:c>
     </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="13" t="str">
+        <x:v>FR-015</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="str">
+        <x:v>통합 Repository 동기화</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="str">
+        <x:v>Pull 및 Commit+Push는 1~6번 폴더와 루트 실행 파일을 포함한 현재 Git Repository 전체 변경사항을 대상으로 해야 한다.</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="str">
+        <x:v>MUST</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="str">
+        <x:v>BoardRepo/6번 폴더 변경 후 Push-Pull 시험</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
@@ -2078,7 +2225,7 @@
         <x:v>현재 Release</x:v>
       </x:c>
       <x:c r="C10" s="38" t="str">
-        <x:v>본 명세가 포함된 Version Manager Release는 260809_3로 정의한다.</x:v>
+        <x:v>본 명세가 포함된 Version Manager Release는 260810_1로 정의한다.</x:v>
       </x:c>
       <x:c r="D10" s="38" t="str">
         <x:v>MUST</x:v>
@@ -2781,6 +2928,40 @@
         <x:v>업데이트 적용 시험</x:v>
       </x:c>
     </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="13" t="str">
+        <x:v>OPS-011</x:v>
+      </x:c>
+      <x:c r="B14" s="13" t="str">
+        <x:v>통합 폴더 전환</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="str">
+        <x:v>기존 git 폴더와 기존 BoardRepo 폴더는 즉시 삭제하지 않고, 새 '자동화 프로그램' 폴더를 별도로 구성한 뒤 1~4번 자료를 단계적으로 이동/검증한다.</x:v>
+      </x:c>
+      <x:c r="D14" s="13" t="str">
+        <x:v>MUST</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="str">
+        <x:v>전환 절차 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="13" t="str">
+        <x:v>OPS-012</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="str">
+        <x:v>BoardRepo 공용자료 사용</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="str">
+        <x:v>통합 후 BoardRepo는 공용 1~4번 폴더를 직접 사용하므로 기존 게시판 자동업로드 폴더의 별도 1~4번 복제본은 운영하지 않는다.</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="str">
+        <x:v>MUST</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="str">
+        <x:v>BoardRepo 업로드 파일 확인</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
